--- a/data/trans_orig/IP04D$colectiva-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73813</t>
+          <t>74144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>83841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81093</t>
+          <t>81100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88023</t>
+          <t>87917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157504</t>
+          <t>157756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170393</t>
+          <t>170767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91853</t>
+          <t>91852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89034</t>
+          <t>88638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95363</t>
+          <t>95342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178160</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186025</t>
+          <t>186361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80969</t>
+          <t>81166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82585</t>
+          <t>81620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166423</t>
+          <t>166120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172368</t>
+          <t>172349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198865</t>
+          <t>198820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204847</t>
+          <t>204839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214100</t>
+          <t>214699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223459</t>
+          <t>223566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416227</t>
+          <t>416939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>426945</t>
+          <t>427398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137545</t>
+          <t>137528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145369</t>
+          <t>145361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135983</t>
+          <t>135958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276409</t>
+          <t>276216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284898</t>
+          <t>284621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66958</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>73344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118592</t>
+          <t>118963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126474</t>
+          <t>126459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32352</t>
+          <t>31717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>34530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>55707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643093</t>
+          <t>643728</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658992</t>
+          <t>659382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>685530</t>
+          <t>686065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>701089</t>
+          <t>701986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1334123</t>
+          <t>1335089</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1356541</t>
+          <t>1356266</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71049</t>
+          <t>71215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79720</t>
+          <t>79517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83922</t>
+          <t>83916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93769</t>
+          <t>93410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158230</t>
+          <t>157894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171452</t>
+          <t>171235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95625</t>
+          <t>95072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>102354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99248</t>
+          <t>98922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107957</t>
+          <t>107761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197400</t>
+          <t>197480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208195</t>
+          <t>208737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54471</t>
+          <t>54454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>61083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71382</t>
+          <t>71635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128666</t>
+          <t>128525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135198</t>
+          <t>135192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212404</t>
+          <t>212124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220779</t>
+          <t>220746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201971</t>
+          <t>201311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207981</t>
+          <t>207995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416574</t>
+          <t>417194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427336</t>
+          <t>427185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130230</t>
+          <t>130567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136274</t>
+          <t>136347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141779</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270377</t>
+          <t>269902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276544</t>
+          <t>276535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55824</t>
+          <t>56180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60477</t>
+          <t>60486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>62171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122001</t>
+          <t>121127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127599</t>
+          <t>127615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17420</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>32832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61368</t>
+          <t>61708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636867</t>
+          <t>636293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652126</t>
+          <t>652012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670966</t>
+          <t>672072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687511</t>
+          <t>687717</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313083</t>
+          <t>1312743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1335417</t>
+          <t>1336264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27852</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46820</t>
+          <t>47943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75617</t>
+          <t>75487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89704</t>
+          <t>89852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111644</t>
+          <t>112122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124775</t>
+          <t>124925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192899</t>
+          <t>191776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211867</t>
+          <t>210726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82913</t>
+          <t>83218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91283</t>
+          <t>91575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82530</t>
+          <t>82665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91375</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168852</t>
+          <t>168952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180859</t>
+          <t>181109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45196</t>
+          <t>44938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50808</t>
+          <t>50936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>53339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61129</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101223</t>
+          <t>101181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110890</t>
+          <t>110989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20427</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>37823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197046</t>
+          <t>196412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210119</t>
+          <t>210132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197845</t>
+          <t>196330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210156</t>
+          <t>209634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398613</t>
+          <t>398274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>417037</t>
+          <t>417025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111485</t>
+          <t>112130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117816</t>
+          <t>117727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154232</t>
+          <t>153944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161296</t>
+          <t>161225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268248</t>
+          <t>269077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277820</t>
+          <t>278044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>61129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>64074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70767</t>
+          <t>70892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128261</t>
+          <t>128359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137289</t>
+          <t>137271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40177</t>
+          <t>40282</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64471</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40296</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64148</t>
+          <t>62687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86079</t>
+          <t>88109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119803</t>
+          <t>120083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592682</t>
+          <t>592577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>616976</t>
+          <t>616871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683427</t>
+          <t>684888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>707279</t>
+          <t>708866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1284925</t>
+          <t>1284645</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1318649</t>
+          <t>1316619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$colectiva-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10174</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6092</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15789</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16607</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8663</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85488</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>81180</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88118</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>79759</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74144</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83841</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>73326</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>83838</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85488</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>81100</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87917</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157756</t>
+          <t>157631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170767</t>
+          <t>170323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2527</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6202</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3606</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8140</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93172</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88474</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95350</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>89948</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>86273</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91852</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>86111</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>91850</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93172</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88638</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95342</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178359</t>
+          <t>177743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186361</t>
+          <t>186118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,67 +1413,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4421</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1422</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4991</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5270</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85517</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82469</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84735</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81166</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>81227</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,28%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85517</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81620</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,93%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>247</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166120</t>
+          <t>166106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172349</t>
+          <t>172286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7731</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3245</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7288</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3912</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12779</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>219747</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>213629</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>223276</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>202863</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>198820</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>204839</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>198905</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>204883</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>219747</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>214699</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>223566</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416939</t>
+          <t>415928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427398</t>
+          <t>426714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4763</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5093</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9493</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139048</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135640</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>142461</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>137528</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>145361</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>138061</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145535</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139048</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>135958</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276216</t>
+          <t>275993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284621</t>
+          <t>284860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6929</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3922</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3521</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8224</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71406</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>67109</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>73358</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>52427</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>49295</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>49696</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,51%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>71406</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>65814</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>73344</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>88,89%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>178</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>118460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126459</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14395</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29740</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>23251</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>16063</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>31717</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>16912</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>32063</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>13365</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>29286</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34530</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55707</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>694379</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>685611</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>700956</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>652194</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>643728</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>659382</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>643382</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>658533</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,56%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>694379</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>686065</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>701986</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1335089</t>
+          <t>1334230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1356266</t>
+          <t>1356862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>976</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9451</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15402</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6898</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11875</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11699</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9451</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5628</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15122</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89587</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>93900</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>76192</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>71215</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79517</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79647</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89587</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83916</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>93410</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157894</t>
+          <t>158282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171235</t>
+          <t>171109</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4783</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9349</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9250</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7874</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4315</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13154</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104202</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98489</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107840</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>99638</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95072</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>102354</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95171</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>102287</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>104202</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>98922</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>107761</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197480</t>
+          <t>196970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208737</t>
+          <t>208516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2982</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7386</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74090</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58858</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>54454</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>61083</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55043</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>61088</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>89,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>98,78%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74090</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71635</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>199</t>
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128525</t>
+          <t>128534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135192</t>
+          <t>135203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6254</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11453</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11091</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,8%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7451</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205776</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201767</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207974</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>217323</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>212124</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>220746</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>212486</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>220203</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,2%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205776</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201311</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207995</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>417194</t>
+          <t>417321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427185</t>
+          <t>426949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1423</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4964</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4374</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2212</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6076</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140211</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136108</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141769</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>134108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130567</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>131157</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,95%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140211</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136347</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>141769</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269902</t>
+          <t>269864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276535</t>
+          <t>276608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4397</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1936</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4907</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5182</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5654</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>66417</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>63428</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>59151</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>56180</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>60486</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>55905</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>60487</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>96,83%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>66417</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>62171</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121127</t>
+          <t>121426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127615</t>
+          <t>127622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17413</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>33109</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>24275</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>17534</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33253</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>17086</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>33340</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>24622</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>17187</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>32832</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61708</t>
+          <t>61349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>680282</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>671795</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>687491</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>975</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>645271</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>636293</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>652012</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>636206</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>652460</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,37%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,03%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>680282</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>672072</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>687717</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312743</t>
+          <t>1313102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1336264</t>
+          <t>1335523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5646,52 +5646,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14531</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21366</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14610</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37242</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47943</t>
+          <t>46189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106470</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>99635</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111793</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>83398</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75487</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>89852</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119080</t>
+          <t>81688</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112122</t>
+          <t>73023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124925</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>202477</t>
+          <t>188158</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191776</t>
+          <t>177739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210726</t>
+          <t>196123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7183</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3755</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13175</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6549</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3106</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11463</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,27 +6410,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>21052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84215</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78223</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87643</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>88132</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>83218</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91575</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87784</t>
+          <t>89806</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82665</t>
+          <t>84718</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91743</t>
+          <t>93462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>175916</t>
+          <t>174021</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168952</t>
+          <t>166892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181109</t>
+          <t>178985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5019</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9437</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6923</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51922</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47504</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54597</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>48846</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>44938</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>50936</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58209</t>
+          <t>50489</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>52428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>107055</t>
+          <t>102410</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101181</t>
+          <t>96040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110989</t>
+          <t>105727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12619</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7855</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19323</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7694</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21414</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37823</t>
+          <t>36288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>189325</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>182621</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>194089</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>203731</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196412</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>210132</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>204908</t>
+          <t>164191</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196330</t>
+          <t>157621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209634</t>
+          <t>169327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>408638</t>
+          <t>353517</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398274</t>
+          <t>344240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>417025</t>
+          <t>360677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7478</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7298</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12968</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>144863</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>140765</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147003</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>115717</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112130</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117727</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>158912</t>
+          <t>115030</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153944</t>
+          <t>111066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161225</t>
+          <t>117240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>274629</t>
+          <t>259893</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269077</t>
+          <t>254901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278044</t>
+          <t>263078</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5865</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1544</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7766</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>65707</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>62422</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67558</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>65204</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>61129</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>67351</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>68546</t>
+          <t>66498</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64074</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70892</t>
+          <t>68755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>133750</t>
+          <t>132205</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128359</t>
+          <t>126958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137271</t>
+          <t>135304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>45312</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>35283</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>56632</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>40282</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>64576</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>41957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62687</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>102262</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120083</t>
+          <t>115794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>642502</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>631182</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>652531</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>847</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>605028</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>592577</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>616871</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>697438</t>
+          <t>567703</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>684888</t>
+          <t>553770</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>708866</t>
+          <t>578670</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1302466</t>
+          <t>1210205</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1284645</t>
+          <t>1192647</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316619</t>
+          <t>1223189</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
